--- a/docs/pension_data_combined_2026-06-22.xlsx
+++ b/docs/pension_data_combined_2026-06-22.xlsx
@@ -1354,7 +1354,7 @@
         <v>1.2109</v>
       </c>
       <c r="D55" t="n">
-        <v>68303175.61</v>
+        <v>68319265.97</v>
       </c>
     </row>
   </sheetData>
